--- a/config/_tables/Logic/#Effect-实体效果-100.xlsx
+++ b/config/_tables/Logic/#Effect-实体效果-100.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23750" windowHeight="13230"/>
+    <workbookView windowWidth="18040" windowHeight="13030"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -40,12 +40,21 @@
     <t>order</t>
   </si>
   <si>
+    <t>parameters</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>Logic.EffectParamBase</t>
+  </si>
+  <si>
+    <t>$type</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -53,17 +62,27 @@
   </si>
   <si>
     <t>执行序列</t>
+  </si>
+  <si>
+    <t>Logic.EffectAttack</t>
+  </si>
+  <si>
+    <t>Logic.EffectHurt</t>
+  </si>
+  <si>
+    <t>Logic.EffectInputMove</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -668,9 +687,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -983,54 +1008,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="12.8181818181818"/>
+    <col min="2" max="2" width="16.2727272727273" style="1"/>
+    <col min="4" max="4" width="30.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="1">
+        <v>100000001</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="1">
+        <v>100000002</v>
+      </c>
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+      <c r="D6" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="B4">
-        <v>100111222</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+    <row r="7" spans="1:8">
+      <c r="B7" s="1">
+        <v>100000003</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
